--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.04613177817727</v>
+        <v>6.344996413953806</v>
       </c>
       <c r="D2" t="n">
-        <v>39.17788523442866</v>
+        <v>6.366406350594659</v>
       </c>
       <c r="E2" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F2" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.6755973679664</v>
+        <v>12.78478457229454</v>
       </c>
       <c r="D3" t="n">
-        <v>40.19233372307716</v>
+        <v>6.531254230000039</v>
       </c>
       <c r="E3" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F3" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.73422883366159</v>
+        <v>9.869312185470008</v>
       </c>
       <c r="D4" t="n">
-        <v>60.86279874913383</v>
+        <v>9.890204796734247</v>
       </c>
       <c r="E4" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F4" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.53583664911628</v>
+        <v>6.587073455481395</v>
       </c>
       <c r="D5" t="n">
-        <v>40.43672883653063</v>
+        <v>6.570968435936228</v>
       </c>
       <c r="E5" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F5" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.74229645563418</v>
+        <v>11.17062317404055</v>
       </c>
       <c r="D6" t="n">
-        <v>44.29106914767649</v>
+        <v>7.197298736497429</v>
       </c>
       <c r="E6" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F6" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>79.26240338489421</v>
+        <v>12.88014055004531</v>
       </c>
       <c r="D7" t="n">
-        <v>78.2167887567613</v>
+        <v>12.71022817297371</v>
       </c>
       <c r="E7" t="n">
-        <v>16.36329591787181</v>
+        <v>2.65903558665417</v>
       </c>
       <c r="F7" t="n">
-        <v>14.43295554947258</v>
+        <v>2.345355276789294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
